--- a/drg/menaka dd/excel for calculation/wall load calculation.xlsx
+++ b/drg/menaka dd/excel for calculation/wall load calculation.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5258AD77-4E6E-421F-BA46-07A0A3DEF33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B8DC3D-DD3C-4E42-A49F-4F90B523965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,6 +12,9 @@
     <sheet name="wall load" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'wall load'!$K$20:$P$27</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>y-y1=((y2-y1)/(x2-x1))*(x-x1)</t>
   </si>
@@ -124,13 +127,61 @@
   </si>
   <si>
     <t>With 25% opening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parapet wall load </t>
+  </si>
+  <si>
+    <t>Wall</t>
+  </si>
+  <si>
+    <t>Unit: KN/m</t>
+  </si>
+  <si>
+    <t>opening</t>
+  </si>
+  <si>
+    <t>Unit:KN/m</t>
+  </si>
+  <si>
+    <t>resting on beam GF &amp;FF</t>
+  </si>
+  <si>
+    <t>resting on beam SF &amp; above</t>
+  </si>
+  <si>
+    <t>resting on slab GF &amp; FF</t>
+  </si>
+  <si>
+    <t>resting on slab SF &amp; above</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WL </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(without opening)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="\ 0%"/>
+    <numFmt numFmtId="165" formatCode="&quot; WL (with&quot;\ 0%\ &quot;opening)&quot;\ &quot;Unit: KN&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;''&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0&quot;''&quot;"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,16 +197,83 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -178,11 +296,358 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -194,23 +659,147 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -534,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF5F103-52A0-4D11-811D-43BFE2FAABA8}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -544,14 +1133,19 @@
     <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -560,20 +1154,20 @@
       <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="9"/>
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
@@ -586,210 +1180,210 @@
       <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8" t="s">
+      <c r="H2" s="28"/>
+      <c r="I2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="8"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="23">
         <v>19.2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="23">
         <v>0.23</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="23">
         <f>E14</f>
         <v>2.8448000000000002</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="23">
         <f>E15</f>
         <v>3.0733999999999999</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="24">
         <f>D3*E3*C3</f>
         <v>12.562636800000002</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="24">
         <f>D3*F3*C3</f>
         <v>13.572134399999999</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="24">
         <f>0.75*G3</f>
         <v>9.4219776000000017</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="24">
         <f>0.75*H3</f>
         <v>10.179100800000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2">
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26">
         <f>E16</f>
         <v>2.54</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="26">
         <f>E17</f>
         <v>2.7686000000000002</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="27">
         <f>D3*E4*C3</f>
         <v>11.21664</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="27">
         <f>D3*F4*C3</f>
         <v>12.226137600000001</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="27">
         <f>0.75*G4</f>
         <v>8.4124800000000004</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="27">
         <f>0.75*H4</f>
         <v>9.169603200000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="23">
         <v>19.2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="23">
         <v>0.115</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="23">
         <f>E3</f>
         <v>2.8448000000000002</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="23">
         <f>F3</f>
         <v>3.0733999999999999</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="24">
         <f>D6*E6*C6</f>
         <v>6.2813184000000009</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="24">
         <f>D6*F6*C6</f>
         <v>6.7860671999999997</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="24">
         <f>0.75*G6</f>
         <v>4.7109888000000009</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="24">
         <f>0.75*H6</f>
         <v>5.0895504000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2">
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26">
         <f>E4</f>
         <v>2.54</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="26">
         <f>F4</f>
         <v>2.7686000000000002</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="27">
         <f>D6*E7*C6</f>
         <v>5.60832</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="27">
         <f>D6*F7*C6</f>
         <v>6.1130688000000006</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="27">
         <f>0.75*G7</f>
         <v>4.2062400000000002</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="27">
         <f>0.75*H7</f>
         <v>4.5848016000000005</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="12">
         <v>19.2</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="12">
         <v>0.115</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="13">
         <f>E18</f>
         <v>0.91439999999999999</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12">
+      <c r="F9" s="13"/>
+      <c r="G9" s="14">
         <f>D9*E9*C9</f>
         <v>2.0189952</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="16"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="7"/>
       <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
@@ -801,7 +1395,6 @@
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="10"/>
       <c r="D14" s="1">
         <f>9*12+4</f>
         <v>112</v>
@@ -831,7 +1424,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D17" s="1">
         <f>9*12+1</f>
         <v>109</v>
@@ -841,7 +1434,7 @@
         <v>2.7686000000000002</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D18" s="1">
         <f>3*12</f>
         <v>36</v>
@@ -851,19 +1444,177 @@
         <v>0.91439999999999999</v>
       </c>
     </row>
+    <row r="19" spans="4:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="K20" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="M20" s="36"/>
+      <c r="N20" s="54">
+        <v>0.25</v>
+      </c>
+      <c r="O20" s="55"/>
+      <c r="P20" s="37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="33"/>
+      <c r="L21" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="M21" s="29"/>
+      <c r="N21" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="O21" s="56"/>
+      <c r="P21" s="30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="34"/>
+      <c r="L22" s="41" t="str">
+        <f>A3</f>
+        <v>230mm</v>
+      </c>
+      <c r="M22" s="31" t="str">
+        <f>A6</f>
+        <v>115mm</v>
+      </c>
+      <c r="N22" s="41" t="str">
+        <f>+L22</f>
+        <v>230mm</v>
+      </c>
+      <c r="O22" s="31" t="str">
+        <f>+M22</f>
+        <v>115mm</v>
+      </c>
+      <c r="P22" s="31" t="str">
+        <f>+M22</f>
+        <v>115mm</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="47">
+        <f>G3</f>
+        <v>12.562636800000002</v>
+      </c>
+      <c r="M23" s="48">
+        <f>G6</f>
+        <v>6.2813184000000009</v>
+      </c>
+      <c r="N23" s="48">
+        <f>I3</f>
+        <v>9.4219776000000017</v>
+      </c>
+      <c r="O23" s="49">
+        <f>I6</f>
+        <v>4.7109888000000009</v>
+      </c>
+      <c r="P23" s="39">
+        <f>G9</f>
+        <v>2.0189952</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" s="51">
+        <f>G4</f>
+        <v>11.21664</v>
+      </c>
+      <c r="M24" s="52">
+        <f>G7</f>
+        <v>5.60832</v>
+      </c>
+      <c r="N24" s="52">
+        <f>I4</f>
+        <v>8.4124800000000004</v>
+      </c>
+      <c r="O24" s="53">
+        <f>I7</f>
+        <v>4.2062400000000002</v>
+      </c>
+      <c r="P24" s="40"/>
+    </row>
+    <row r="25" spans="4:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="43"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="40"/>
+    </row>
+    <row r="26" spans="4:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="L26" s="47">
+        <f>H3</f>
+        <v>13.572134399999999</v>
+      </c>
+      <c r="M26" s="48">
+        <f>H6</f>
+        <v>6.7860671999999997</v>
+      </c>
+      <c r="N26" s="48">
+        <f>J3</f>
+        <v>10.179100800000001</v>
+      </c>
+      <c r="O26" s="49">
+        <f>J6</f>
+        <v>5.0895504000000003</v>
+      </c>
+      <c r="P26" s="40"/>
+    </row>
+    <row r="27" spans="4:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="L27" s="59">
+        <f>H4</f>
+        <v>12.226137600000001</v>
+      </c>
+      <c r="M27" s="60">
+        <f>H7</f>
+        <v>6.1130688000000006</v>
+      </c>
+      <c r="N27" s="60">
+        <f>J4</f>
+        <v>9.169603200000001</v>
+      </c>
+      <c r="O27" s="61">
+        <f>J7</f>
+        <v>4.5848016000000005</v>
+      </c>
+      <c r="P27" s="42"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="G9:H9"/>
+  <mergeCells count="12">
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P23:P27"/>
+    <mergeCell ref="K20:K22"/>
     <mergeCell ref="E9:F9"/>
-    <mergeCell ref="I9:J9"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="G9:J9"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
